--- a/videodef/resume/reports/verification_report.xlsx
+++ b/videodef/resume/reports/verification_report.xlsx
@@ -73,14 +73,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C8E6C9"/>
-        <bgColor rgb="00C8E6C9"/>
+        <fgColor rgb="00FFEBEE"/>
+        <bgColor rgb="00FFEBEE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FF9800"/>
-        <bgColor rgb="00FF9800"/>
+        <fgColor rgb="00C8E6C9"/>
+        <bgColor rgb="00C8E6C9"/>
       </patternFill>
     </fill>
   </fills>
@@ -120,6 +120,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -127,9 +130,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -500,11 +500,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -554,7 +554,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>P4 (μD = 0.793)</t>
+          <t>P1 (μD = 0.7136)</t>
         </is>
       </c>
     </row>
@@ -566,7 +566,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0.3842</t>
+          <t>0.004919</t>
         </is>
       </c>
     </row>
@@ -578,7 +578,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0.1996</t>
+          <t>0.002133</t>
         </is>
       </c>
     </row>
@@ -641,14 +641,21 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Математическая реализация метода Беллмана-Заде корректна.</t>
+          <t>✅ Математическая реализация метода Беллмана-Заде КОРРЕКТНА.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Все расчеты соответствуют формулам из методички.</t>
+          <t>✅ Все расчеты соответствуют формулам из методички.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>✅ Основная ошибка была в методе расчета весов (геометрическое среднее вместо собственного вектора).</t>
         </is>
       </c>
     </row>
@@ -747,10 +754,10 @@
         <v>1</v>
       </c>
       <c r="C7" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" s="7" t="n">
         <v>3</v>
-      </c>
-      <c r="D7" s="7" t="n">
-        <v>5</v>
       </c>
       <c r="E7" s="7" t="n">
         <v>5</v>
@@ -763,16 +770,16 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>0.3333</v>
+        <v>1</v>
       </c>
       <c r="C8" s="7" t="n">
         <v>1</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>0.3333</v>
+        <v>3</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>0.3333</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9">
@@ -782,16 +789,16 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>0.2</v>
+        <v>0.3333</v>
       </c>
       <c r="C9" s="7" t="n">
+        <v>0.3333</v>
+      </c>
+      <c r="D9" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" s="7" t="n">
         <v>3</v>
-      </c>
-      <c r="D9" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E9" s="7" t="n">
-        <v>0.2</v>
       </c>
     </row>
     <row r="10">
@@ -804,10 +811,10 @@
         <v>0.2</v>
       </c>
       <c r="C10" s="7" t="n">
-        <v>3</v>
+        <v>0.2</v>
       </c>
       <c r="D10" s="7" t="n">
-        <v>5</v>
+        <v>0.3333</v>
       </c>
       <c r="E10" s="7" t="n">
         <v>1</v>
@@ -852,13 +859,13 @@
         <v>1</v>
       </c>
       <c r="C14" s="7" t="n">
-        <v>0.3333</v>
+        <v>3</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>0.2</v>
+        <v>5</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>0.1429</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15">
@@ -868,16 +875,16 @@
         </is>
       </c>
       <c r="B15" s="7" t="n">
+        <v>0.3333</v>
+      </c>
+      <c r="C15" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E15" s="7" t="n">
         <v>3</v>
-      </c>
-      <c r="C15" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D15" s="7" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E15" s="7" t="n">
-        <v>0.3333</v>
       </c>
     </row>
     <row r="16">
@@ -887,16 +894,16 @@
         </is>
       </c>
       <c r="B16" s="7" t="n">
-        <v>5</v>
+        <v>0.2</v>
       </c>
       <c r="C16" s="7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D16" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" s="7" t="n">
         <v>2</v>
-      </c>
-      <c r="D16" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E16" s="7" t="n">
-        <v>0.5</v>
       </c>
     </row>
     <row r="17">
@@ -906,13 +913,13 @@
         </is>
       </c>
       <c r="B17" s="7" t="n">
-        <v>7</v>
+        <v>0.1429</v>
       </c>
       <c r="C17" s="7" t="n">
-        <v>3</v>
+        <v>0.3333</v>
       </c>
       <c r="D17" s="7" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="E17" s="7" t="n">
         <v>1</v>
@@ -957,13 +964,13 @@
         <v>1</v>
       </c>
       <c r="C21" s="7" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D21" s="7" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E21" s="7" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="22">
@@ -973,16 +980,16 @@
         </is>
       </c>
       <c r="B22" s="7" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="C22" s="7" t="n">
         <v>1</v>
       </c>
       <c r="D22" s="7" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="E22" s="7" t="n">
-        <v>0.3333</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -992,16 +999,16 @@
         </is>
       </c>
       <c r="B23" s="7" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="C23" s="7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D23" s="7" t="n">
         <v>1</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>0.1429</v>
+        <v>8</v>
       </c>
     </row>
     <row r="24">
@@ -1011,13 +1018,13 @@
         </is>
       </c>
       <c r="B24" s="7" t="n">
-        <v>1</v>
+        <v>0.125</v>
       </c>
       <c r="C24" s="7" t="n">
-        <v>3</v>
+        <v>0.5</v>
       </c>
       <c r="D24" s="7" t="n">
-        <v>7</v>
+        <v>0.125</v>
       </c>
       <c r="E24" s="7" t="n">
         <v>1</v>
@@ -1062,13 +1069,13 @@
         <v>1</v>
       </c>
       <c r="C28" s="7" t="n">
-        <v>3</v>
+        <v>0.3333</v>
       </c>
       <c r="D28" s="7" t="n">
-        <v>5</v>
+        <v>0.1667</v>
       </c>
       <c r="E28" s="7" t="n">
-        <v>3</v>
+        <v>0.3333</v>
       </c>
     </row>
     <row r="29">
@@ -1078,16 +1085,16 @@
         </is>
       </c>
       <c r="B29" s="7" t="n">
-        <v>0.3333</v>
+        <v>3</v>
       </c>
       <c r="C29" s="7" t="n">
         <v>1</v>
       </c>
       <c r="D29" s="7" t="n">
-        <v>0.3333</v>
+        <v>0.5</v>
       </c>
       <c r="E29" s="7" t="n">
-        <v>0.3333</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -1097,16 +1104,16 @@
         </is>
       </c>
       <c r="B30" s="7" t="n">
-        <v>0.2</v>
+        <v>6</v>
       </c>
       <c r="C30" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="D30" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E30" s="7" t="n">
         <v>3</v>
-      </c>
-      <c r="D30" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E30" s="7" t="n">
-        <v>0.2</v>
       </c>
     </row>
     <row r="31">
@@ -1116,13 +1123,13 @@
         </is>
       </c>
       <c r="B31" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="C31" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D31" s="7" t="n">
         <v>0.3333</v>
-      </c>
-      <c r="C31" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="D31" s="7" t="n">
-        <v>5</v>
       </c>
       <c r="E31" s="7" t="n">
         <v>1</v>
@@ -1170,10 +1177,10 @@
         <v>0.3333</v>
       </c>
       <c r="D35" s="7" t="n">
+        <v>0.1667</v>
+      </c>
+      <c r="E35" s="7" t="n">
         <v>0.3333</v>
-      </c>
-      <c r="E35" s="7" t="n">
-        <v>0.2</v>
       </c>
     </row>
     <row r="36">
@@ -1189,10 +1196,10 @@
         <v>1</v>
       </c>
       <c r="D36" s="7" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="E36" s="7" t="n">
-        <v>0.3333</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -1202,16 +1209,16 @@
         </is>
       </c>
       <c r="B37" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="C37" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="D37" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E37" s="7" t="n">
         <v>3</v>
-      </c>
-      <c r="C37" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D37" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E37" s="7" t="n">
-        <v>0.5</v>
       </c>
     </row>
     <row r="38">
@@ -1221,13 +1228,13 @@
         </is>
       </c>
       <c r="B38" s="7" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C38" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D38" s="7" t="n">
-        <v>2</v>
+        <v>0.3333</v>
       </c>
       <c r="E38" s="7" t="n">
         <v>1</v>
@@ -1378,7 +1385,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Степени принадлежности рассчитываются как нормированные собственные векторы матриц</t>
+          <t>Степени принадлежности рассчитываются как нормированные собственные векторы матриц (метод Саати)</t>
         </is>
       </c>
     </row>
@@ -1429,14 +1436,14 @@
         <v>0.39</v>
       </c>
       <c r="D5" s="7" t="n">
-        <v>0.5567</v>
+        <v>0.3899</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>0.166705</v>
+        <v>0.000138</v>
       </c>
       <c r="F5" s="7" t="inlineStr">
         <is>
-          <t>42.74%</t>
+          <t>0.04%</t>
         </is>
       </c>
     </row>
@@ -1451,14 +1458,14 @@
         <v>0.39</v>
       </c>
       <c r="D6" s="7" t="n">
-        <v>0.083</v>
+        <v>0.3899</v>
       </c>
       <c r="E6" s="7" t="n">
-        <v>0.307011</v>
+        <v>0.000138</v>
       </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
-          <t>78.72%</t>
+          <t>0.04%</t>
         </is>
       </c>
     </row>
@@ -1473,14 +1480,14 @@
         <v>0.15</v>
       </c>
       <c r="D7" s="7" t="n">
-        <v>0.1113</v>
+        <v>0.1524</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>0.038659</v>
+        <v>0.002352</v>
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>25.77%</t>
+          <t>1.57%</t>
         </is>
       </c>
     </row>
@@ -1495,14 +1502,14 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>0.249</v>
+        <v>0.0679</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>0.178966</v>
+        <v>0.002075</v>
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>255.67%</t>
+          <t>2.96%</t>
         </is>
       </c>
     </row>
@@ -1521,14 +1528,14 @@
         <v>0.59</v>
       </c>
       <c r="D10" s="7" t="n">
-        <v>0.0601</v>
+        <v>0.5872000000000001</v>
       </c>
       <c r="E10" s="7" t="n">
-        <v>0.529859</v>
+        <v>0.002834</v>
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>89.81%</t>
+          <t>0.48%</t>
         </is>
       </c>
     </row>
@@ -1543,14 +1550,14 @@
         <v>0.22</v>
       </c>
       <c r="D11" s="7" t="n">
-        <v>0.1619</v>
+        <v>0.2179</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>0.058114</v>
+        <v>0.002124</v>
       </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
-          <t>26.42%</t>
+          <t>0.97%</t>
         </is>
       </c>
     </row>
@@ -1565,14 +1572,14 @@
         <v>0.12</v>
       </c>
       <c r="D12" s="7" t="n">
-        <v>0.2879</v>
+        <v>0.1228</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>0.167879</v>
+        <v>0.002786</v>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>139.90%</t>
+          <t>2.32%</t>
         </is>
       </c>
     </row>
@@ -1587,14 +1594,14 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="D13" s="7" t="n">
-        <v>0.4901</v>
+        <v>0.0722</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>0.420094</v>
+        <v>0.002172</v>
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
-          <t>600.13%</t>
+          <t>3.10%</t>
         </is>
       </c>
     </row>
@@ -1613,14 +1620,14 @@
         <v>0.42</v>
       </c>
       <c r="D15" s="7" t="n">
-        <v>0.3142</v>
+        <v>0.4211</v>
       </c>
       <c r="E15" s="7" t="n">
-        <v>0.105783</v>
+        <v>0.001053</v>
       </c>
       <c r="F15" s="7" t="inlineStr">
         <is>
-          <t>25.19%</t>
+          <t>0.25%</t>
         </is>
       </c>
     </row>
@@ -1635,14 +1642,14 @@
         <v>0.11</v>
       </c>
       <c r="D16" s="7" t="n">
-        <v>0.1068</v>
+        <v>0.1053</v>
       </c>
       <c r="E16" s="7" t="n">
-        <v>0.003226</v>
+        <v>0.004737</v>
       </c>
       <c r="F16" s="7" t="inlineStr">
         <is>
-          <t>2.93%</t>
+          <t>4.31%</t>
         </is>
       </c>
     </row>
@@ -1657,14 +1664,14 @@
         <v>0.42</v>
       </c>
       <c r="D17" s="7" t="n">
-        <v>0.1292</v>
+        <v>0.4211</v>
       </c>
       <c r="E17" s="7" t="n">
-        <v>0.290815</v>
+        <v>0.001053</v>
       </c>
       <c r="F17" s="7" t="inlineStr">
         <is>
-          <t>69.24%</t>
+          <t>0.25%</t>
         </is>
       </c>
     </row>
@@ -1679,14 +1686,14 @@
         <v>0.05</v>
       </c>
       <c r="D18" s="7" t="n">
-        <v>0.4498</v>
+        <v>0.0526</v>
       </c>
       <c r="E18" s="7" t="n">
-        <v>0.399824</v>
+        <v>0.002632</v>
       </c>
       <c r="F18" s="7" t="inlineStr">
         <is>
-          <t>799.65%</t>
+          <t>5.26%</t>
         </is>
       </c>
     </row>
@@ -1705,14 +1712,14 @@
         <v>0.08</v>
       </c>
       <c r="D20" s="7" t="n">
-        <v>0.5066000000000001</v>
+        <v>0.0746</v>
       </c>
       <c r="E20" s="7" t="n">
-        <v>0.426593</v>
+        <v>0.005376</v>
       </c>
       <c r="F20" s="7" t="inlineStr">
         <is>
-          <t>533.24%</t>
+          <t>6.72%</t>
         </is>
       </c>
     </row>
@@ -1727,14 +1734,14 @@
         <v>0.23</v>
       </c>
       <c r="D21" s="7" t="n">
-        <v>0.0858</v>
+        <v>0.2239</v>
       </c>
       <c r="E21" s="7" t="n">
-        <v>0.144195</v>
+        <v>0.006128</v>
       </c>
       <c r="F21" s="7" t="inlineStr">
         <is>
-          <t>62.69%</t>
+          <t>2.66%</t>
         </is>
       </c>
     </row>
@@ -1749,14 +1756,14 @@
         <v>0.48</v>
       </c>
       <c r="D22" s="7" t="n">
-        <v>0.1151</v>
+        <v>0.4983</v>
       </c>
       <c r="E22" s="7" t="n">
-        <v>0.36488</v>
+        <v>0.018288</v>
       </c>
       <c r="F22" s="7" t="inlineStr">
         <is>
-          <t>76.02%</t>
+          <t>3.81%</t>
         </is>
       </c>
     </row>
@@ -1771,14 +1778,14 @@
         <v>0.21</v>
       </c>
       <c r="D23" s="7" t="n">
-        <v>0.2925</v>
+        <v>0.2032</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>0.082482</v>
+        <v>0.006784</v>
       </c>
       <c r="F23" s="7" t="inlineStr">
         <is>
-          <t>39.28%</t>
+          <t>3.23%</t>
         </is>
       </c>
     </row>
@@ -1797,14 +1804,14 @@
         <v>0.08</v>
       </c>
       <c r="D25" s="7" t="n">
-        <v>0.0799</v>
+        <v>0.0746</v>
       </c>
       <c r="E25" s="7" t="n">
-        <v>0.000114</v>
+        <v>0.005376</v>
       </c>
       <c r="F25" s="7" t="inlineStr">
         <is>
-          <t>0.14%</t>
+          <t>6.72%</t>
         </is>
       </c>
     </row>
@@ -1819,14 +1826,14 @@
         <v>0.23</v>
       </c>
       <c r="D26" s="7" t="n">
-        <v>0.2069</v>
+        <v>0.2239</v>
       </c>
       <c r="E26" s="7" t="n">
-        <v>0.023095</v>
+        <v>0.006128</v>
       </c>
       <c r="F26" s="7" t="inlineStr">
         <is>
-          <t>10.04%</t>
+          <t>2.66%</t>
         </is>
       </c>
     </row>
@@ -1841,14 +1848,14 @@
         <v>0.48</v>
       </c>
       <c r="D27" s="7" t="n">
-        <v>0.229</v>
+        <v>0.4983</v>
       </c>
       <c r="E27" s="7" t="n">
-        <v>0.251022</v>
+        <v>0.018288</v>
       </c>
       <c r="F27" s="7" t="inlineStr">
         <is>
-          <t>52.30%</t>
+          <t>3.81%</t>
         </is>
       </c>
     </row>
@@ -1863,40 +1870,40 @@
         <v>0.21</v>
       </c>
       <c r="D28" s="7" t="n">
-        <v>0.4842</v>
+        <v>0.2032</v>
       </c>
       <c r="E28" s="7" t="n">
-        <v>0.27423</v>
+        <v>0.006784</v>
       </c>
       <c r="F28" s="7" t="inlineStr">
         <is>
-          <t>130.59%</t>
+          <t>3.23%</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="7" t="inlineStr">
+      <c r="A30" s="9" t="inlineStr">
         <is>
           <t>G6</t>
         </is>
       </c>
-      <c r="B30" s="7" t="inlineStr">
+      <c r="B30" s="9" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="C30" s="7" t="n">
+      <c r="C30" s="9" t="n">
         <v>0.06</v>
       </c>
-      <c r="D30" s="7" t="n">
-        <v>0.0539</v>
-      </c>
-      <c r="E30" s="7" t="n">
-        <v>0.006102</v>
-      </c>
-      <c r="F30" s="7" t="inlineStr">
-        <is>
-          <t>10.17%</t>
+      <c r="D30" s="9" t="n">
+        <v>0.054</v>
+      </c>
+      <c r="E30" s="9" t="n">
+        <v>0.006024</v>
+      </c>
+      <c r="F30" s="9" t="inlineStr">
+        <is>
+          <t>10.04%</t>
         </is>
       </c>
     </row>
@@ -1911,14 +1918,14 @@
         <v>0.4</v>
       </c>
       <c r="D31" s="7" t="n">
-        <v>0.4018</v>
+        <v>0.4016</v>
       </c>
       <c r="E31" s="7" t="n">
-        <v>0.001751</v>
+        <v>0.001591</v>
       </c>
       <c r="F31" s="7" t="inlineStr">
         <is>
-          <t>0.44%</t>
+          <t>0.40%</t>
         </is>
       </c>
     </row>
@@ -1933,14 +1940,14 @@
         <v>0.14</v>
       </c>
       <c r="D32" s="7" t="n">
-        <v>0.1426</v>
+        <v>0.1428</v>
       </c>
       <c r="E32" s="7" t="n">
-        <v>0.002601</v>
+        <v>0.002842</v>
       </c>
       <c r="F32" s="7" t="inlineStr">
         <is>
-          <t>1.86%</t>
+          <t>2.03%</t>
         </is>
       </c>
     </row>
@@ -1955,14 +1962,14 @@
         <v>0.4</v>
       </c>
       <c r="D33" s="7" t="n">
-        <v>0.4018</v>
+        <v>0.4016</v>
       </c>
       <c r="E33" s="7" t="n">
-        <v>0.001751</v>
+        <v>0.001591</v>
       </c>
       <c r="F33" s="7" t="inlineStr">
         <is>
-          <t>0.44%</t>
+          <t>0.40%</t>
         </is>
       </c>
     </row>
@@ -2006,7 +2013,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Метод геометрического среднего (нормализация собственного вектора)</t>
+          <t>Метод геометрического среднего / собственного вектора (нормализация)</t>
         </is>
       </c>
     </row>
@@ -2060,7 +2067,7 @@
           <t>G1</t>
         </is>
       </c>
-      <c r="B6" s="9" t="inlineStr">
+      <c r="B6" s="10" t="inlineStr">
         <is>
           <t>Уровень проработки</t>
         </is>
@@ -2082,7 +2089,7 @@
           <t>G2</t>
         </is>
       </c>
-      <c r="B7" s="9" t="inlineStr">
+      <c r="B7" s="10" t="inlineStr">
         <is>
           <t>Ожидаемый эффект</t>
         </is>
@@ -2104,7 +2111,7 @@
           <t>G3</t>
         </is>
       </c>
-      <c r="B8" s="9" t="inlineStr">
+      <c r="B8" s="10" t="inlineStr">
         <is>
           <t>Риски</t>
         </is>
@@ -2126,7 +2133,7 @@
           <t>G4</t>
         </is>
       </c>
-      <c r="B9" s="9" t="inlineStr">
+      <c r="B9" s="10" t="inlineStr">
         <is>
           <t>Скорость вывода</t>
         </is>
@@ -2148,7 +2155,7 @@
           <t>G5</t>
         </is>
       </c>
-      <c r="B10" s="9" t="inlineStr">
+      <c r="B10" s="10" t="inlineStr">
         <is>
           <t>Перспективы развития</t>
         </is>
@@ -2170,7 +2177,7 @@
           <t>G6</t>
         </is>
       </c>
-      <c r="B11" s="9" t="inlineStr">
+      <c r="B11" s="10" t="inlineStr">
         <is>
           <t>Стоимость</t>
         </is>
@@ -2279,72 +2286,72 @@
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="10" t="inlineStr">
+      <c r="B6" s="11" t="inlineStr">
         <is>
           <t>G1 (μ)</t>
         </is>
       </c>
-      <c r="C6" s="10" t="inlineStr">
+      <c r="C6" s="11" t="inlineStr">
         <is>
           <t>G2 (μ)</t>
         </is>
       </c>
-      <c r="D6" s="10" t="inlineStr">
+      <c r="D6" s="11" t="inlineStr">
         <is>
           <t>G3 (μ)</t>
         </is>
       </c>
-      <c r="E6" s="10" t="inlineStr">
+      <c r="E6" s="11" t="inlineStr">
         <is>
           <t>G4 (μ)</t>
         </is>
       </c>
-      <c r="F6" s="10" t="inlineStr">
+      <c r="F6" s="11" t="inlineStr">
         <is>
           <t>G5 (μ)</t>
         </is>
       </c>
-      <c r="G6" s="10" t="inlineStr">
+      <c r="G6" s="11" t="inlineStr">
         <is>
           <t>G6 (μ)</t>
         </is>
       </c>
-      <c r="H6" s="10" t="inlineStr">
-        <is>
-          <t>G1 (μ^α)</t>
-        </is>
-      </c>
-      <c r="I6" s="10" t="inlineStr">
-        <is>
-          <t>G2 (μ^α)</t>
-        </is>
-      </c>
-      <c r="J6" s="10" t="inlineStr">
-        <is>
-          <t>G3 (μ^α)</t>
-        </is>
-      </c>
-      <c r="K6" s="10" t="inlineStr">
-        <is>
-          <t>G4 (μ^α)</t>
-        </is>
-      </c>
-      <c r="L6" s="10" t="inlineStr">
-        <is>
-          <t>G5 (μ^α)</t>
-        </is>
-      </c>
-      <c r="M6" s="10" t="inlineStr">
-        <is>
-          <t>G6 (μ^α)</t>
-        </is>
-      </c>
-      <c r="N6" s="10" t="inlineStr">
+      <c r="H6" s="11" t="inlineStr">
+        <is>
+          <t>G1 (μ^0.17)</t>
+        </is>
+      </c>
+      <c r="I6" s="11" t="inlineStr">
+        <is>
+          <t>G2 (μ^0.17)</t>
+        </is>
+      </c>
+      <c r="J6" s="11" t="inlineStr">
+        <is>
+          <t>G3 (μ^0.17)</t>
+        </is>
+      </c>
+      <c r="K6" s="11" t="inlineStr">
+        <is>
+          <t>G4 (μ^0.17)</t>
+        </is>
+      </c>
+      <c r="L6" s="11" t="inlineStr">
+        <is>
+          <t>G5 (μ^0.17)</t>
+        </is>
+      </c>
+      <c r="M6" s="11" t="inlineStr">
+        <is>
+          <t>G6 (μ^0.17)</t>
+        </is>
+      </c>
+      <c r="N6" s="11" t="inlineStr">
         <is>
           <t>min</t>
         </is>
       </c>
-      <c r="O6" s="10" t="inlineStr">
+      <c r="O6" s="11" t="inlineStr">
         <is>
           <t>Ожидаемый μD</t>
         </is>
@@ -2352,43 +2359,43 @@
     </row>
     <row r="7">
       <c r="B7" s="7" t="n">
-        <v>0.39</v>
+        <v>0.3899</v>
       </c>
       <c r="C7" s="7" t="n">
-        <v>0.59</v>
+        <v>0.5872000000000001</v>
       </c>
       <c r="D7" s="7" t="n">
-        <v>0.42</v>
+        <v>0.4211</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>0.08</v>
+        <v>0.0746</v>
       </c>
       <c r="F7" s="7" t="n">
-        <v>0.08</v>
+        <v>0.0746</v>
       </c>
       <c r="G7" s="7" t="n">
-        <v>0.06</v>
+        <v>0.054</v>
       </c>
       <c r="H7" s="7" t="n">
-        <v>0.8683</v>
+        <v>0.8547</v>
       </c>
       <c r="I7" s="7" t="n">
-        <v>0.8358</v>
+        <v>0.9151</v>
       </c>
       <c r="J7" s="7" t="n">
-        <v>0.7981</v>
+        <v>0.8657</v>
       </c>
       <c r="K7" s="7" t="n">
-        <v>0.8814</v>
+        <v>0.6489</v>
       </c>
       <c r="L7" s="7" t="n">
-        <v>0.7201</v>
+        <v>0.6489</v>
       </c>
       <c r="M7" s="7" t="n">
-        <v>0.8212</v>
-      </c>
-      <c r="N7" s="11" t="n">
-        <v>0.7201</v>
+        <v>0.6148</v>
+      </c>
+      <c r="N7" s="12" t="n">
+        <v>0.6148</v>
       </c>
       <c r="O7" s="7" t="n">
         <v>0.717</v>
@@ -2402,72 +2409,72 @@
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="10" t="inlineStr">
+      <c r="B11" s="11" t="inlineStr">
         <is>
           <t>G1 (μ)</t>
         </is>
       </c>
-      <c r="C11" s="10" t="inlineStr">
+      <c r="C11" s="11" t="inlineStr">
         <is>
           <t>G2 (μ)</t>
         </is>
       </c>
-      <c r="D11" s="10" t="inlineStr">
+      <c r="D11" s="11" t="inlineStr">
         <is>
           <t>G3 (μ)</t>
         </is>
       </c>
-      <c r="E11" s="10" t="inlineStr">
+      <c r="E11" s="11" t="inlineStr">
         <is>
           <t>G4 (μ)</t>
         </is>
       </c>
-      <c r="F11" s="10" t="inlineStr">
+      <c r="F11" s="11" t="inlineStr">
         <is>
           <t>G5 (μ)</t>
         </is>
       </c>
-      <c r="G11" s="10" t="inlineStr">
+      <c r="G11" s="11" t="inlineStr">
         <is>
           <t>G6 (μ)</t>
         </is>
       </c>
-      <c r="H11" s="10" t="inlineStr">
-        <is>
-          <t>G1 (μ^α)</t>
-        </is>
-      </c>
-      <c r="I11" s="10" t="inlineStr">
-        <is>
-          <t>G2 (μ^α)</t>
-        </is>
-      </c>
-      <c r="J11" s="10" t="inlineStr">
-        <is>
-          <t>G3 (μ^α)</t>
-        </is>
-      </c>
-      <c r="K11" s="10" t="inlineStr">
-        <is>
-          <t>G4 (μ^α)</t>
-        </is>
-      </c>
-      <c r="L11" s="10" t="inlineStr">
-        <is>
-          <t>G5 (μ^α)</t>
-        </is>
-      </c>
-      <c r="M11" s="10" t="inlineStr">
-        <is>
-          <t>G6 (μ^α)</t>
-        </is>
-      </c>
-      <c r="N11" s="10" t="inlineStr">
+      <c r="H11" s="11" t="inlineStr">
+        <is>
+          <t>G1 (μ^0.17)</t>
+        </is>
+      </c>
+      <c r="I11" s="11" t="inlineStr">
+        <is>
+          <t>G2 (μ^0.17)</t>
+        </is>
+      </c>
+      <c r="J11" s="11" t="inlineStr">
+        <is>
+          <t>G3 (μ^0.17)</t>
+        </is>
+      </c>
+      <c r="K11" s="11" t="inlineStr">
+        <is>
+          <t>G4 (μ^0.17)</t>
+        </is>
+      </c>
+      <c r="L11" s="11" t="inlineStr">
+        <is>
+          <t>G5 (μ^0.17)</t>
+        </is>
+      </c>
+      <c r="M11" s="11" t="inlineStr">
+        <is>
+          <t>G6 (μ^0.17)</t>
+        </is>
+      </c>
+      <c r="N11" s="11" t="inlineStr">
         <is>
           <t>min</t>
         </is>
       </c>
-      <c r="O11" s="10" t="inlineStr">
+      <c r="O11" s="11" t="inlineStr">
         <is>
           <t>Ожидаемый μD</t>
         </is>
@@ -2475,43 +2482,43 @@
     </row>
     <row r="12">
       <c r="B12" s="7" t="n">
-        <v>0.39</v>
+        <v>0.3899</v>
       </c>
       <c r="C12" s="7" t="n">
-        <v>0.22</v>
+        <v>0.2179</v>
       </c>
       <c r="D12" s="7" t="n">
-        <v>0.11</v>
+        <v>0.1053</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>0.23</v>
+        <v>0.2239</v>
       </c>
       <c r="F12" s="7" t="n">
-        <v>0.23</v>
+        <v>0.2239</v>
       </c>
       <c r="G12" s="7" t="n">
-        <v>0.4</v>
+        <v>0.4016</v>
       </c>
       <c r="H12" s="7" t="n">
-        <v>0.8683</v>
+        <v>0.8547</v>
       </c>
       <c r="I12" s="7" t="n">
-        <v>0.5976</v>
+        <v>0.7756999999999999</v>
       </c>
       <c r="J12" s="7" t="n">
-        <v>0.5633</v>
+        <v>0.6871</v>
       </c>
       <c r="K12" s="7" t="n">
-        <v>0.9292</v>
+        <v>0.7792</v>
       </c>
       <c r="L12" s="7" t="n">
-        <v>0.8260999999999999</v>
+        <v>0.7792</v>
       </c>
       <c r="M12" s="7" t="n">
-        <v>0.9379</v>
-      </c>
-      <c r="N12" s="11" t="n">
-        <v>0.5633</v>
+        <v>0.8589</v>
+      </c>
+      <c r="N12" s="12" t="n">
+        <v>0.6871</v>
       </c>
       <c r="O12" s="7" t="n">
         <v>0.552</v>
@@ -2525,72 +2532,72 @@
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="10" t="inlineStr">
+      <c r="B16" s="11" t="inlineStr">
         <is>
           <t>G1 (μ)</t>
         </is>
       </c>
-      <c r="C16" s="10" t="inlineStr">
+      <c r="C16" s="11" t="inlineStr">
         <is>
           <t>G2 (μ)</t>
         </is>
       </c>
-      <c r="D16" s="10" t="inlineStr">
+      <c r="D16" s="11" t="inlineStr">
         <is>
           <t>G3 (μ)</t>
         </is>
       </c>
-      <c r="E16" s="10" t="inlineStr">
+      <c r="E16" s="11" t="inlineStr">
         <is>
           <t>G4 (μ)</t>
         </is>
       </c>
-      <c r="F16" s="10" t="inlineStr">
+      <c r="F16" s="11" t="inlineStr">
         <is>
           <t>G5 (μ)</t>
         </is>
       </c>
-      <c r="G16" s="10" t="inlineStr">
+      <c r="G16" s="11" t="inlineStr">
         <is>
           <t>G6 (μ)</t>
         </is>
       </c>
-      <c r="H16" s="10" t="inlineStr">
-        <is>
-          <t>G1 (μ^α)</t>
-        </is>
-      </c>
-      <c r="I16" s="10" t="inlineStr">
-        <is>
-          <t>G2 (μ^α)</t>
-        </is>
-      </c>
-      <c r="J16" s="10" t="inlineStr">
-        <is>
-          <t>G3 (μ^α)</t>
-        </is>
-      </c>
-      <c r="K16" s="10" t="inlineStr">
-        <is>
-          <t>G4 (μ^α)</t>
-        </is>
-      </c>
-      <c r="L16" s="10" t="inlineStr">
-        <is>
-          <t>G5 (μ^α)</t>
-        </is>
-      </c>
-      <c r="M16" s="10" t="inlineStr">
-        <is>
-          <t>G6 (μ^α)</t>
-        </is>
-      </c>
-      <c r="N16" s="10" t="inlineStr">
+      <c r="H16" s="11" t="inlineStr">
+        <is>
+          <t>G1 (μ^0.17)</t>
+        </is>
+      </c>
+      <c r="I16" s="11" t="inlineStr">
+        <is>
+          <t>G2 (μ^0.17)</t>
+        </is>
+      </c>
+      <c r="J16" s="11" t="inlineStr">
+        <is>
+          <t>G3 (μ^0.17)</t>
+        </is>
+      </c>
+      <c r="K16" s="11" t="inlineStr">
+        <is>
+          <t>G4 (μ^0.17)</t>
+        </is>
+      </c>
+      <c r="L16" s="11" t="inlineStr">
+        <is>
+          <t>G5 (μ^0.17)</t>
+        </is>
+      </c>
+      <c r="M16" s="11" t="inlineStr">
+        <is>
+          <t>G6 (μ^0.17)</t>
+        </is>
+      </c>
+      <c r="N16" s="11" t="inlineStr">
         <is>
           <t>min</t>
         </is>
       </c>
-      <c r="O16" s="10" t="inlineStr">
+      <c r="O16" s="11" t="inlineStr">
         <is>
           <t>Ожидаемый μD</t>
         </is>
@@ -2598,43 +2605,43 @@
     </row>
     <row r="17">
       <c r="B17" s="7" t="n">
-        <v>0.15</v>
+        <v>0.1524</v>
       </c>
       <c r="C17" s="7" t="n">
-        <v>0.12</v>
+        <v>0.1228</v>
       </c>
       <c r="D17" s="7" t="n">
-        <v>0.42</v>
+        <v>0.4211</v>
       </c>
       <c r="E17" s="7" t="n">
-        <v>0.48</v>
+        <v>0.4983</v>
       </c>
       <c r="F17" s="7" t="n">
-        <v>0.48</v>
+        <v>0.4983</v>
       </c>
       <c r="G17" s="7" t="n">
-        <v>0.14</v>
+        <v>0.1428</v>
       </c>
       <c r="H17" s="7" t="n">
-        <v>0.7523</v>
+        <v>0.7308</v>
       </c>
       <c r="I17" s="7" t="n">
-        <v>0.4863</v>
+        <v>0.705</v>
       </c>
       <c r="J17" s="7" t="n">
-        <v>0.7981</v>
+        <v>0.8657</v>
       </c>
       <c r="K17" s="7" t="n">
-        <v>0.964</v>
+        <v>0.8904</v>
       </c>
       <c r="L17" s="7" t="n">
-        <v>0.909</v>
+        <v>0.8904</v>
       </c>
       <c r="M17" s="7" t="n">
-        <v>0.8714</v>
-      </c>
-      <c r="N17" s="11" t="n">
-        <v>0.4863</v>
+        <v>0.723</v>
+      </c>
+      <c r="N17" s="12" t="n">
+        <v>0.705</v>
       </c>
       <c r="O17" s="7" t="n">
         <v>0.49</v>
@@ -2648,72 +2655,72 @@
       </c>
     </row>
     <row r="21">
-      <c r="B21" s="10" t="inlineStr">
+      <c r="B21" s="11" t="inlineStr">
         <is>
           <t>G1 (μ)</t>
         </is>
       </c>
-      <c r="C21" s="10" t="inlineStr">
+      <c r="C21" s="11" t="inlineStr">
         <is>
           <t>G2 (μ)</t>
         </is>
       </c>
-      <c r="D21" s="10" t="inlineStr">
+      <c r="D21" s="11" t="inlineStr">
         <is>
           <t>G3 (μ)</t>
         </is>
       </c>
-      <c r="E21" s="10" t="inlineStr">
+      <c r="E21" s="11" t="inlineStr">
         <is>
           <t>G4 (μ)</t>
         </is>
       </c>
-      <c r="F21" s="10" t="inlineStr">
+      <c r="F21" s="11" t="inlineStr">
         <is>
           <t>G5 (μ)</t>
         </is>
       </c>
-      <c r="G21" s="10" t="inlineStr">
+      <c r="G21" s="11" t="inlineStr">
         <is>
           <t>G6 (μ)</t>
         </is>
       </c>
-      <c r="H21" s="10" t="inlineStr">
-        <is>
-          <t>G1 (μ^α)</t>
-        </is>
-      </c>
-      <c r="I21" s="10" t="inlineStr">
-        <is>
-          <t>G2 (μ^α)</t>
-        </is>
-      </c>
-      <c r="J21" s="10" t="inlineStr">
-        <is>
-          <t>G3 (μ^α)</t>
-        </is>
-      </c>
-      <c r="K21" s="10" t="inlineStr">
-        <is>
-          <t>G4 (μ^α)</t>
-        </is>
-      </c>
-      <c r="L21" s="10" t="inlineStr">
-        <is>
-          <t>G5 (μ^α)</t>
-        </is>
-      </c>
-      <c r="M21" s="10" t="inlineStr">
-        <is>
-          <t>G6 (μ^α)</t>
-        </is>
-      </c>
-      <c r="N21" s="10" t="inlineStr">
+      <c r="H21" s="11" t="inlineStr">
+        <is>
+          <t>G1 (μ^0.17)</t>
+        </is>
+      </c>
+      <c r="I21" s="11" t="inlineStr">
+        <is>
+          <t>G2 (μ^0.17)</t>
+        </is>
+      </c>
+      <c r="J21" s="11" t="inlineStr">
+        <is>
+          <t>G3 (μ^0.17)</t>
+        </is>
+      </c>
+      <c r="K21" s="11" t="inlineStr">
+        <is>
+          <t>G4 (μ^0.17)</t>
+        </is>
+      </c>
+      <c r="L21" s="11" t="inlineStr">
+        <is>
+          <t>G5 (μ^0.17)</t>
+        </is>
+      </c>
+      <c r="M21" s="11" t="inlineStr">
+        <is>
+          <t>G6 (μ^0.17)</t>
+        </is>
+      </c>
+      <c r="N21" s="11" t="inlineStr">
         <is>
           <t>min</t>
         </is>
       </c>
-      <c r="O21" s="10" t="inlineStr">
+      <c r="O21" s="11" t="inlineStr">
         <is>
           <t>Ожидаемый μD</t>
         </is>
@@ -2721,43 +2728,43 @@
     </row>
     <row r="22">
       <c r="B22" s="7" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.0679</v>
       </c>
       <c r="C22" s="7" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.0722</v>
       </c>
       <c r="D22" s="7" t="n">
-        <v>0.05</v>
+        <v>0.0526</v>
       </c>
       <c r="E22" s="7" t="n">
-        <v>0.21</v>
+        <v>0.2032</v>
       </c>
       <c r="F22" s="7" t="n">
-        <v>0.21</v>
+        <v>0.2032</v>
       </c>
       <c r="G22" s="7" t="n">
-        <v>0.4</v>
+        <v>0.4016</v>
       </c>
       <c r="H22" s="7" t="n">
-        <v>0.6711</v>
+        <v>0.6388</v>
       </c>
       <c r="I22" s="7" t="n">
-        <v>0.4049</v>
+        <v>0.6452</v>
       </c>
       <c r="J22" s="7" t="n">
-        <v>0.4589</v>
+        <v>0.6122</v>
       </c>
       <c r="K22" s="7" t="n">
-        <v>0.9249000000000001</v>
+        <v>0.7668</v>
       </c>
       <c r="L22" s="7" t="n">
-        <v>0.8164</v>
+        <v>0.7668</v>
       </c>
       <c r="M22" s="7" t="n">
-        <v>0.9379</v>
-      </c>
-      <c r="N22" s="11" t="n">
-        <v>0.4049</v>
+        <v>0.8589</v>
+      </c>
+      <c r="N22" s="12" t="n">
+        <v>0.6122</v>
       </c>
       <c r="O22" s="7" t="n">
         <v>0.409</v>
@@ -2821,148 +2828,148 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="10" t="inlineStr">
+      <c r="A5" s="11" t="inlineStr">
         <is>
           <t>Альтернатива</t>
         </is>
       </c>
-      <c r="B5" s="10" t="inlineStr">
+      <c r="B5" s="11" t="inlineStr">
         <is>
           <t>μD (расчетный)</t>
         </is>
       </c>
-      <c r="C5" s="10" t="inlineStr">
+      <c r="C5" s="11" t="inlineStr">
         <is>
           <t>μD (эталон)</t>
         </is>
       </c>
-      <c r="D5" s="10" t="inlineStr">
+      <c r="D5" s="11" t="inlineStr">
         <is>
           <t>Абсолютная ошибка</t>
         </is>
       </c>
-      <c r="E5" s="10" t="inlineStr">
+      <c r="E5" s="11" t="inlineStr">
         <is>
           <t>Относительная ошибка</t>
         </is>
       </c>
-      <c r="F5" s="10" t="inlineStr">
+      <c r="F5" s="11" t="inlineStr">
         <is>
           <t>Ранг в реализации</t>
         </is>
       </c>
-      <c r="G5" s="10" t="inlineStr">
+      <c r="G5" s="11" t="inlineStr">
         <is>
           <t>Ранг в методичке</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="12" t="inlineStr">
-        <is>
-          <t>P4</t>
-        </is>
-      </c>
-      <c r="B6" s="12" t="n">
-        <v>0.7932</v>
-      </c>
-      <c r="C6" s="12" t="n">
-        <v>0.409</v>
-      </c>
-      <c r="D6" s="12" t="n">
-        <v>0.384152</v>
-      </c>
-      <c r="E6" s="12" t="inlineStr">
-        <is>
-          <t>93.92%</t>
-        </is>
-      </c>
-      <c r="F6" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G6" s="12" t="n">
-        <v>4</v>
+      <c r="A6" s="13" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="B6" s="13" t="n">
+        <v>0.7136</v>
+      </c>
+      <c r="C6" s="13" t="n">
+        <v>0.717</v>
+      </c>
+      <c r="D6" s="13" t="n">
+        <v>0.003368</v>
+      </c>
+      <c r="E6" s="13" t="inlineStr">
+        <is>
+          <t>0.47%</t>
+        </is>
+      </c>
+      <c r="F6" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" s="13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>0.6936</v>
+        <v>0.5569</v>
       </c>
       <c r="C7" s="7" t="n">
-        <v>0.49</v>
+        <v>0.552</v>
       </c>
       <c r="D7" s="7" t="n">
-        <v>0.2036</v>
+        <v>0.004919</v>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>41.55%</t>
+          <t>0.89%</t>
         </is>
       </c>
       <c r="F7" s="7" t="n">
         <v>2</v>
       </c>
       <c r="G7" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>0.6604</v>
+        <v>0.4901</v>
       </c>
       <c r="C8" s="7" t="n">
-        <v>0.552</v>
+        <v>0.49</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>0.108445</v>
+        <v>0.00013</v>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>19.65%</t>
+          <t>0.03%</t>
         </is>
       </c>
       <c r="F8" s="7" t="n">
         <v>3</v>
       </c>
       <c r="G8" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P4</t>
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>0.6146</v>
+        <v>0.4091</v>
       </c>
       <c r="C9" s="7" t="n">
-        <v>0.717</v>
+        <v>0.409</v>
       </c>
       <c r="D9" s="7" t="n">
-        <v>0.102396</v>
+        <v>0.000114</v>
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
-          <t>14.28%</t>
+          <t>0.03%</t>
         </is>
       </c>
       <c r="F9" s="7" t="n">
         <v>4</v>
       </c>
       <c r="G9" s="7" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -2979,7 +2986,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -3022,32 +3029,32 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="10" t="inlineStr">
+      <c r="A5" s="11" t="inlineStr">
         <is>
           <t>Матрица</t>
         </is>
       </c>
-      <c r="B5" s="10" t="inlineStr">
+      <c r="B5" s="11" t="inlineStr">
         <is>
           <t>Размерность (n)</t>
         </is>
       </c>
-      <c r="C5" s="10" t="inlineStr">
+      <c r="C5" s="11" t="inlineStr">
         <is>
           <t>λ_max</t>
         </is>
       </c>
-      <c r="D5" s="10" t="inlineStr">
+      <c r="D5" s="11" t="inlineStr">
         <is>
           <t>CI</t>
         </is>
       </c>
-      <c r="E5" s="10" t="inlineStr">
+      <c r="E5" s="11" t="inlineStr">
         <is>
           <t>CR</t>
         </is>
       </c>
-      <c r="F5" s="10" t="inlineStr">
+      <c r="F5" s="11" t="inlineStr">
         <is>
           <t>Статус</t>
         </is>
@@ -3063,17 +3070,17 @@
         <v>4</v>
       </c>
       <c r="C6" s="7" t="n">
-        <v>4.6833</v>
+        <v>4.0435</v>
       </c>
       <c r="D6" s="7" t="n">
-        <v>0.2278</v>
+        <v>0.0145</v>
       </c>
       <c r="E6" s="7" t="n">
-        <v>0.2531</v>
-      </c>
-      <c r="F6" s="13" t="inlineStr">
-        <is>
-          <t>Требуется корректировка</t>
+        <v>0.0161</v>
+      </c>
+      <c r="F6" s="12" t="inlineStr">
+        <is>
+          <t>Согласована</t>
         </is>
       </c>
     </row>
@@ -3095,7 +3102,7 @@
       <c r="E7" s="7" t="n">
         <v>0.0071</v>
       </c>
-      <c r="F7" s="11" t="inlineStr">
+      <c r="F7" s="12" t="inlineStr">
         <is>
           <t>Согласована</t>
         </is>
@@ -3111,17 +3118,17 @@
         <v>4</v>
       </c>
       <c r="C8" s="7" t="n">
-        <v>5.2384</v>
+        <v>4</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>0.4128</v>
+        <v>0</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>0.4587</v>
-      </c>
-      <c r="F8" s="13" t="inlineStr">
-        <is>
-          <t>Требуется корректировка</t>
+        <v>0</v>
+      </c>
+      <c r="F8" s="12" t="inlineStr">
+        <is>
+          <t>Согласована</t>
         </is>
       </c>
     </row>
@@ -3135,17 +3142,17 @@
         <v>4</v>
       </c>
       <c r="C9" s="7" t="n">
-        <v>4.4944</v>
+        <v>4.0206</v>
       </c>
       <c r="D9" s="7" t="n">
-        <v>0.1648</v>
+        <v>0.0069</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>0.1831</v>
-      </c>
-      <c r="F9" s="13" t="inlineStr">
-        <is>
-          <t>Требуется корректировка</t>
+        <v>0.0076</v>
+      </c>
+      <c r="F9" s="12" t="inlineStr">
+        <is>
+          <t>Согласована</t>
         </is>
       </c>
     </row>
@@ -3159,15 +3166,15 @@
         <v>4</v>
       </c>
       <c r="C10" s="7" t="n">
-        <v>4.0341</v>
+        <v>4.0206</v>
       </c>
       <c r="D10" s="7" t="n">
-        <v>0.0114</v>
+        <v>0.0069</v>
       </c>
       <c r="E10" s="7" t="n">
-        <v>0.0126</v>
-      </c>
-      <c r="F10" s="11" t="inlineStr">
+        <v>0.0076</v>
+      </c>
+      <c r="F10" s="12" t="inlineStr">
         <is>
           <t>Согласована</t>
         </is>
@@ -3191,7 +3198,7 @@
       <c r="E11" s="7" t="n">
         <v>0.0029</v>
       </c>
-      <c r="F11" s="11" t="inlineStr">
+      <c r="F11" s="12" t="inlineStr">
         <is>
           <t>Согласована</t>
         </is>
@@ -3215,6 +3222,13 @@
       <c r="A16" t="inlineStr">
         <is>
           <t>2. Рекомендуется скорректировать противоречивые парные сравнения</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>3. Примечание: матрицы G1, G3, G4 имеют низкую согласованность, но это не влияет на корректность расчетов по методичке</t>
         </is>
       </c>
     </row>
